--- a/artfynd/A 20013-2023 artfynd.xlsx
+++ b/artfynd/A 20013-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20013-2023 artfynd.xlsx
+++ b/artfynd/A 20013-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98538819</v>
+        <v>98538377</v>
       </c>
       <c r="B2" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206002</v>
+        <v>100015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577698.3603600838</v>
+        <v>577699</v>
       </c>
       <c r="R2" t="n">
-        <v>6325323.081585385</v>
+        <v>6325323</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,22 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,15 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98538352</v>
+        <v>63184302</v>
       </c>
       <c r="B3" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,26 +812,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>100051</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Sydfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Eptesicus serotinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,6 +839,11 @@
           <t>registreringar</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -856,7 +851,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -865,13 +860,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577698.3603600838</v>
+        <v>577774</v>
       </c>
       <c r="R3" t="n">
-        <v>6325323.081585385</v>
+        <v>6325650</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,22 +890,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>2012-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2012-06-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lokal-ID: 8 Box-ID: 8E</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,54 +915,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Alexander Eriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Amie Ringberg, Alexander Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98539675</v>
+        <v>98537513</v>
       </c>
       <c r="B4" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>100051</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Sydfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus serotinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -996,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577698.3603600838</v>
+        <v>577699</v>
       </c>
       <c r="R4" t="n">
-        <v>6325323.081585385</v>
+        <v>6325323</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1068,15 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98539872</v>
+        <v>63201017</v>
       </c>
       <c r="B5" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1083,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1111,6 +1091,11 @@
           <t>registreringar</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1118,7 +1103,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1127,13 +1112,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577698.3603600838</v>
+        <v>577774</v>
       </c>
       <c r="R5" t="n">
-        <v>6325323.081585385</v>
+        <v>6325650</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1157,22 +1142,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-08-30</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>20:00</t>
+          <t>2012-06-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>06:00</t>
+          <t>2012-06-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lokal-ID: 8 Box-ID: 8E</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1187,27 +1167,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Alexander Eriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Amie Ringberg, Alexander Eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98537485</v>
+        <v>98539862</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,26 +1190,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1258,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577698.3603600838</v>
+        <v>577699</v>
       </c>
       <c r="R6" t="n">
-        <v>6325323.081585385</v>
+        <v>6325323</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1288,22 +1263,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-07-26</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,37 +1305,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98537513</v>
+        <v>98537480</v>
       </c>
       <c r="B7" t="n">
-        <v>57485</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Dokumentation efterfrågas</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100051</v>
+        <v>205992</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sydfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus serotinus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1389,10 +1359,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577698.3603600838</v>
+        <v>577699</v>
       </c>
       <c r="R7" t="n">
-        <v>6325323.081585385</v>
+        <v>6325323</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1419,22 +1389,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1461,42 +1431,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98538393</v>
+        <v>98539675</v>
       </c>
       <c r="B8" t="n">
-        <v>57482</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på determinatörs verifiering</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100015</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1520,10 +1485,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577698.3603600838</v>
+        <v>577699</v>
       </c>
       <c r="R8" t="n">
-        <v>6325323.081585385</v>
+        <v>6325323</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1550,22 +1515,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1589,6 +1554,510 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>63189582</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kärnebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>577774</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6325650</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2012-06-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2012-06-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Lokal-ID: 8 Box-ID: 8E</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Amie Ringberg, Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>98538343</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kärnebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>577699</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6325323</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>63225909</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56840</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kärnebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>577774</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6325650</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2012-06-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2012-06-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lokal-ID: 8 Box-ID: 8E</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Amie Ringberg, Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>98538815</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kärnebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>577699</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6325323</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20013-2023 artfynd.xlsx
+++ b/artfynd/A 20013-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538377</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63184302</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98537513</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63201017</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1302,6 +1327,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539862</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1428,6 +1458,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98537480</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1554,6 +1589,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539675</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1680,6 +1720,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63189582</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1806,6 +1851,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538343</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1932,6 +1982,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63225909</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2058,8 +2113,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538815</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>